--- a/output/anova_all_2way_interactions.xlsx
+++ b/output/anova_all_2way_interactions.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.889041341709003</v>
+        <v>9.064967801725768</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04264775886389045</v>
+        <v>0.1012252381016558</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8377851617953749</v>
+        <v>0.7524977342072731</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2963.539755781107</v>
+        <v>2958.659527879923</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>25.85135204521003</v>
+        <v>33.03828780443778</v>
       </c>
       <c r="E3" t="n">
-        <v>1.835500726928417e-05</v>
+        <v>2.518498062523283e-06</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.047569533029514</v>
+        <v>33.96856281329091</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03530748818931684</v>
+        <v>0.379314734917405</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8522180021764807</v>
+        <v>0.5424662298786114</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1997.365478227151</v>
+        <v>2118.833082573962</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>17.42328512376913</v>
+        <v>23.66024766688994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002361388506063837</v>
+        <v>3.168890912810962e-05</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.27309657535765</v>
+        <v>31.3282256821869</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.333861319558749</v>
+        <v>0.3498310389340873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.567706202731119</v>
+        <v>0.5584975866988582</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>291.0331487981242</v>
+        <v>299.0354391966234</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.538720923763444</v>
+        <v>3.339221296268553</v>
       </c>
       <c r="E7" t="n">
-        <v>0.121567844160311</v>
+        <v>0.07728770386634656</v>
       </c>
     </row>
     <row r="8">
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.57113035263788</v>
+        <v>24.10062329934544</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3015685750810286</v>
+        <v>0.2691230002394615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5869653902270042</v>
+        <v>0.6076044415134401</v>
       </c>
     </row>
     <row r="9">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.1264383280237</v>
+        <v>36.37806819707831</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4023670657642716</v>
+        <v>0.406220815723855</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5306770621080665</v>
+        <v>0.528573469821651</v>
       </c>
     </row>
     <row r="10">
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9593667481226136</v>
+        <v>1.917996286219413</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00836868393542073</v>
+        <v>0.02141757532924605</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9277189139994745</v>
+        <v>0.8845946698056407</v>
       </c>
     </row>
     <row r="11">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16227.2409119952</v>
+        <v>16633.1617286459</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>141.5523840097281</v>
+        <v>185.7365401832967</v>
       </c>
       <c r="E11" t="n">
-        <v>6.910905219222463e-13</v>
+        <v>1.239543519150906e-14</v>
       </c>
     </row>
     <row r="12">
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>473.452270842867</v>
+        <v>194.1600878777458</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.129987224327659</v>
+        <v>2.168115933243751</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05106563136448322</v>
+        <v>0.1509798024373498</v>
       </c>
     </row>
     <row r="13">
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1374.67817020162</v>
+        <v>558.0307030268265</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.99150079138405</v>
+        <v>6.23132834196841</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001629526469095594</v>
+        <v>0.01807743891930039</v>
       </c>
     </row>
     <row r="14">
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1105.135305383443</v>
+        <v>638.4409261509943</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.640242477370791</v>
+        <v>7.12924040956578</v>
       </c>
       <c r="E14" t="n">
-        <v>0.004132837936313457</v>
+        <v>0.01196562475370992</v>
       </c>
     </row>
     <row r="15">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40.7142566598121</v>
+        <v>0.06401455919379592</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3551558841478828</v>
+        <v>0.0007148275799866494</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5556790057636847</v>
+        <v>0.9788414678117079</v>
       </c>
     </row>
     <row r="16">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.248044882807281</v>
+        <v>24.67896376191737</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002163728553313699</v>
+        <v>0.2755811203683074</v>
       </c>
       <c r="E16" t="n">
-        <v>0.963207339808819</v>
+        <v>0.6033467254318567</v>
       </c>
     </row>
     <row r="17">
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.67332082501566</v>
+        <v>2.00184807417041</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2588443301634592</v>
+        <v>0.02235391811459751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6146367404999624</v>
+        <v>0.8821179110710071</v>
       </c>
     </row>
     <row r="18">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2386.499050337834</v>
+        <v>1600.030741778861</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>20.81774910746283</v>
+        <v>17.86696834992616</v>
       </c>
       <c r="E18" t="n">
-        <v>7.985649040407733e-05</v>
+        <v>0.0001936765474912663</v>
       </c>
     </row>
     <row r="19">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>399.902989668529</v>
+        <v>401.2433596341252</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.488407047580947</v>
+        <v>4.480540417136423</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07159681681458081</v>
+        <v>0.04241101183842814</v>
       </c>
     </row>
     <row r="20">
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.322380212040813</v>
+        <v>15.53858735318412</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05515096475635364</v>
+        <v>0.1735138214489846</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8159266000888887</v>
+        <v>0.6798778390505535</v>
       </c>
     </row>
     <row r="21">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1960.856153974912</v>
+        <v>1041.072397440279</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>17.10480942512659</v>
+        <v>11.62528137076133</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0002625749010254711</v>
+        <v>0.001824161763035252</v>
       </c>
     </row>
     <row r="22">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>602.7315606818519</v>
+        <v>629.9895215439068</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.257707690119579</v>
+        <v>7.034866611185271</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02903344300477182</v>
+        <v>0.01248740025937189</v>
       </c>
     </row>
     <row r="23">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3439.131249999999</v>
+        <v>2776.125866666667</v>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
